--- a/data/SIAV.MI.xlsx
+++ b/data/SIAV.MI.xlsx
@@ -24315,6 +24315,52 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1042">
+      <c r="A1042" s="1" t="n">
+        <v>46276.2916666667</v>
+      </c>
+      <c r="B1042" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1042" t="n">
+        <v>2.85999989509583</v>
+      </c>
+      <c r="D1042" t="n">
+        <v>2.85999989509583</v>
+      </c>
+      <c r="E1042" t="n">
+        <v>2.85999989509583</v>
+      </c>
+      <c r="F1042" t="n">
+        <v>2.85999989509583</v>
+      </c>
+      <c r="G1042" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1043">
+      <c r="A1043" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B1043" t="n">
+        <v>3500</v>
+      </c>
+      <c r="C1043" t="n">
+        <v>2.8199999332428</v>
+      </c>
+      <c r="D1043" t="n">
+        <v>2.79999995231628</v>
+      </c>
+      <c r="E1043" t="n">
+        <v>2.8199999332428</v>
+      </c>
+      <c r="F1043" t="n">
+        <v>2.79999995231628</v>
+      </c>
+      <c r="G1043" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SIAV.MI.xlsx
+++ b/data/SIAV.MI.xlsx
@@ -24361,6 +24361,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1044">
+      <c r="A1044" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B1044" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C1044" t="n">
+        <v>2.83999991416931</v>
+      </c>
+      <c r="D1044" t="n">
+        <v>2.83999991416931</v>
+      </c>
+      <c r="E1044" t="n">
+        <v>2.83999991416931</v>
+      </c>
+      <c r="F1044" t="n">
+        <v>2.83999991416931</v>
+      </c>
+      <c r="G1044" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SIAV.MI.xlsx
+++ b/data/SIAV.MI.xlsx
@@ -24384,6 +24384,52 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1045">
+      <c r="A1045" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B1045" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1045" t="n">
+        <v>2.83999991416931</v>
+      </c>
+      <c r="D1045" t="n">
+        <v>2.83999991416931</v>
+      </c>
+      <c r="E1045" t="n">
+        <v>2.83999991416931</v>
+      </c>
+      <c r="F1045" t="n">
+        <v>2.83999991416931</v>
+      </c>
+      <c r="G1045" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1046">
+      <c r="A1046" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B1046" t="n">
+        <v>3000</v>
+      </c>
+      <c r="C1046" t="n">
+        <v>2.85999989509583</v>
+      </c>
+      <c r="D1046" t="n">
+        <v>2.85999989509583</v>
+      </c>
+      <c r="E1046" t="n">
+        <v>2.85999989509583</v>
+      </c>
+      <c r="F1046" t="n">
+        <v>2.85999989509583</v>
+      </c>
+      <c r="G1046" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SIAV.MI.xlsx
+++ b/data/SIAV.MI.xlsx
@@ -24248,22 +24248,22 @@
     </row>
     <row r="1039">
       <c r="A1039" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B1039" t="n">
-        <v>3500</v>
+        <v>3000</v>
       </c>
       <c r="C1039" t="n">
-        <v>2.96000003814697</v>
+        <v>2.98000001907349</v>
       </c>
       <c r="D1039" t="n">
-        <v>2.90000009536743</v>
+        <v>2.94000005722046</v>
       </c>
       <c r="E1039" t="n">
         <v>2.96000003814697</v>
       </c>
       <c r="F1039" t="n">
-        <v>2.90000009536743</v>
+        <v>2.98000001907349</v>
       </c>
       <c r="G1039" t="s">
         <v>7</v>
@@ -24271,22 +24271,22 @@
     </row>
     <row r="1040">
       <c r="A1040" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B1040" t="n">
-        <v>2500</v>
+        <v>3500</v>
       </c>
       <c r="C1040" t="n">
-        <v>2.88000011444092</v>
+        <v>2.96000003814697</v>
       </c>
       <c r="D1040" t="n">
-        <v>2.8199999332428</v>
+        <v>2.90000009536743</v>
       </c>
       <c r="E1040" t="n">
-        <v>2.88000011444092</v>
+        <v>2.96000003814697</v>
       </c>
       <c r="F1040" t="n">
-        <v>2.85999989509583</v>
+        <v>2.90000009536743</v>
       </c>
       <c r="G1040" t="s">
         <v>7</v>
@@ -24294,19 +24294,19 @@
     </row>
     <row r="1041">
       <c r="A1041" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B1041" t="n">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="C1041" t="n">
-        <v>2.85999989509583</v>
+        <v>2.88000011444092</v>
       </c>
       <c r="D1041" t="n">
-        <v>2.85999989509583</v>
+        <v>2.8199999332428</v>
       </c>
       <c r="E1041" t="n">
-        <v>2.85999989509583</v>
+        <v>2.88000011444092</v>
       </c>
       <c r="F1041" t="n">
         <v>2.85999989509583</v>
@@ -24317,7 +24317,7 @@
     </row>
     <row r="1042">
       <c r="A1042" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B1042" t="n">
         <v>0</v>
@@ -24340,22 +24340,22 @@
     </row>
     <row r="1043">
       <c r="A1043" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B1043" t="n">
-        <v>3500</v>
+        <v>0</v>
       </c>
       <c r="C1043" t="n">
-        <v>2.8199999332428</v>
+        <v>2.85999989509583</v>
       </c>
       <c r="D1043" t="n">
-        <v>2.79999995231628</v>
+        <v>2.85999989509583</v>
       </c>
       <c r="E1043" t="n">
-        <v>2.8199999332428</v>
+        <v>2.85999989509583</v>
       </c>
       <c r="F1043" t="n">
-        <v>2.79999995231628</v>
+        <v>2.85999989509583</v>
       </c>
       <c r="G1043" t="s">
         <v>7</v>
@@ -24363,22 +24363,22 @@
     </row>
     <row r="1044">
       <c r="A1044" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B1044" t="n">
-        <v>1000</v>
+        <v>3500</v>
       </c>
       <c r="C1044" t="n">
-        <v>2.83999991416931</v>
+        <v>2.8199999332428</v>
       </c>
       <c r="D1044" t="n">
-        <v>2.83999991416931</v>
+        <v>2.79999995231628</v>
       </c>
       <c r="E1044" t="n">
-        <v>2.83999991416931</v>
+        <v>2.8199999332428</v>
       </c>
       <c r="F1044" t="n">
-        <v>2.83999991416931</v>
+        <v>2.79999995231628</v>
       </c>
       <c r="G1044" t="s">
         <v>7</v>
@@ -24386,10 +24386,10 @@
     </row>
     <row r="1045">
       <c r="A1045" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B1045" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="C1045" t="n">
         <v>2.83999991416931</v>
@@ -24409,22 +24409,22 @@
     </row>
     <row r="1046">
       <c r="A1046" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B1046" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="C1046" t="n">
-        <v>2.85999989509583</v>
+        <v>2.83999991416931</v>
       </c>
       <c r="D1046" t="n">
-        <v>2.85999989509583</v>
+        <v>2.83999991416931</v>
       </c>
       <c r="E1046" t="n">
-        <v>2.85999989509583</v>
+        <v>2.83999991416931</v>
       </c>
       <c r="F1046" t="n">
-        <v>2.85999989509583</v>
+        <v>2.83999991416931</v>
       </c>
       <c r="G1046" t="s">
         <v>7</v>

--- a/data/SIAV.MI.xlsx
+++ b/data/SIAV.MI.xlsx
@@ -27649,6 +27649,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1050">
+      <c r="A1050" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B1050" t="n">
+        <v>18500</v>
+      </c>
+      <c r="C1050" t="n">
+        <v>3.09999990463257</v>
+      </c>
+      <c r="D1050" t="n">
+        <v>2.94000005722046</v>
+      </c>
+      <c r="E1050" t="n">
+        <v>2.94000005722046</v>
+      </c>
+      <c r="F1050" t="n">
+        <v>3.01999998092651</v>
+      </c>
+      <c r="G1050" t="n">
+        <v>3.01999998092651</v>
+      </c>
+      <c r="H1050" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SIAV.MI.xlsx
+++ b/data/SIAV.MI.xlsx
@@ -27675,6 +27675,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1051">
+      <c r="A1051" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B1051" t="n">
+        <v>20000</v>
+      </c>
+      <c r="C1051" t="n">
+        <v>3.14000010490417</v>
+      </c>
+      <c r="D1051" t="n">
+        <v>3.01999998092651</v>
+      </c>
+      <c r="E1051" t="n">
+        <v>3.01999998092651</v>
+      </c>
+      <c r="F1051" t="n">
+        <v>3.14000010490417</v>
+      </c>
+      <c r="G1051" t="n">
+        <v>3.14000010490417</v>
+      </c>
+      <c r="H1051" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SIAV.MI.xlsx
+++ b/data/SIAV.MI.xlsx
@@ -27701,6 +27701,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1052">
+      <c r="A1052" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B1052" t="n">
+        <v>20000</v>
+      </c>
+      <c r="C1052" t="n">
+        <v>3.16000008583069</v>
+      </c>
+      <c r="D1052" t="n">
+        <v>3.01999998092651</v>
+      </c>
+      <c r="E1052" t="n">
+        <v>3.16000008583069</v>
+      </c>
+      <c r="F1052" t="n">
+        <v>3.03999996185303</v>
+      </c>
+      <c r="G1052" t="n">
+        <v>3.03999996185303</v>
+      </c>
+      <c r="H1052" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SIAV.MI.xlsx
+++ b/data/SIAV.MI.xlsx
@@ -27727,6 +27727,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1053">
+      <c r="A1053" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B1053" t="n">
+        <v>16000</v>
+      </c>
+      <c r="C1053" t="n">
+        <v>2.96000003814697</v>
+      </c>
+      <c r="D1053" t="n">
+        <v>2.74000000953674</v>
+      </c>
+      <c r="E1053" t="n">
+        <v>2.96000003814697</v>
+      </c>
+      <c r="F1053" t="n">
+        <v>2.83999991416931</v>
+      </c>
+      <c r="G1053" t="n">
+        <v>2.83999991416931</v>
+      </c>
+      <c r="H1053" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SIAV.MI.xlsx
+++ b/data/SIAV.MI.xlsx
@@ -27805,6 +27805,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1056">
+      <c r="A1056" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B1056" t="n">
+        <v>3500</v>
+      </c>
+      <c r="C1056" t="n">
+        <v>2.55999994277954</v>
+      </c>
+      <c r="D1056" t="n">
+        <v>2.51999998092651</v>
+      </c>
+      <c r="E1056" t="n">
+        <v>2.55999994277954</v>
+      </c>
+      <c r="F1056" t="n">
+        <v>2.51999998092651</v>
+      </c>
+      <c r="G1056" t="n">
+        <v>2.51999998092651</v>
+      </c>
+      <c r="H1056" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SIAV.MI.xlsx
+++ b/data/SIAV.MI.xlsx
@@ -24676,7 +24676,9 @@
       <c r="E1057" t="n">
         <v>2.55999994277954</v>
       </c>
-      <c r="F1057"/>
+      <c r="F1057" t="n">
+        <v>2.53999996185303</v>
+      </c>
       <c r="G1057" t="s">
         <v>7</v>
       </c>

--- a/data/SIAV.MI.xlsx
+++ b/data/SIAV.MI.xlsx
@@ -24683,6 +24683,50 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1058">
+      <c r="A1058" s="1" t="n">
+        <v>46297.2916666667</v>
+      </c>
+      <c r="B1058" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1058" t="n">
+        <v>2.53999996185303</v>
+      </c>
+      <c r="D1058" t="n">
+        <v>2.53999996185303</v>
+      </c>
+      <c r="E1058" t="n">
+        <v>2.53999996185303</v>
+      </c>
+      <c r="F1058" t="n">
+        <v>2.53999996185303</v>
+      </c>
+      <c r="G1058" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1059">
+      <c r="A1059" s="1" t="n">
+        <v>46300.2916666667</v>
+      </c>
+      <c r="B1059" t="n">
+        <v>1500</v>
+      </c>
+      <c r="C1059" t="n">
+        <v>2.53999996185303</v>
+      </c>
+      <c r="D1059" t="n">
+        <v>2.53999996185303</v>
+      </c>
+      <c r="E1059" t="n">
+        <v>2.53999996185303</v>
+      </c>
+      <c r="F1059"/>
+      <c r="G1059" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SIAV.MI.xlsx
+++ b/data/SIAV.MI.xlsx
@@ -24722,8 +24722,31 @@
       <c r="E1059" t="n">
         <v>2.53999996185303</v>
       </c>
-      <c r="F1059"/>
+      <c r="F1059" t="n">
+        <v>2.53999996185303</v>
+      </c>
       <c r="G1059" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1060">
+      <c r="A1060" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B1060" t="n">
+        <v>500</v>
+      </c>
+      <c r="C1060" t="n">
+        <v>2.53999996185303</v>
+      </c>
+      <c r="D1060" t="n">
+        <v>2.53999996185303</v>
+      </c>
+      <c r="E1060" t="n">
+        <v>2.53999996185303</v>
+      </c>
+      <c r="F1060"/>
+      <c r="G1060" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/SIAV.MI.xlsx
+++ b/data/SIAV.MI.xlsx
@@ -24745,8 +24745,31 @@
       <c r="E1060" t="n">
         <v>2.53999996185303</v>
       </c>
-      <c r="F1060"/>
+      <c r="F1060" t="n">
+        <v>2.53999996185303</v>
+      </c>
       <c r="G1060" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1061">
+      <c r="A1061" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B1061" t="n">
+        <v>500</v>
+      </c>
+      <c r="C1061" t="n">
+        <v>2.53999996185303</v>
+      </c>
+      <c r="D1061" t="n">
+        <v>2.53999996185303</v>
+      </c>
+      <c r="E1061" t="n">
+        <v>2.53999996185303</v>
+      </c>
+      <c r="F1061"/>
+      <c r="G1061" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/SIAV.MI.xlsx
+++ b/data/SIAV.MI.xlsx
@@ -24768,8 +24768,31 @@
       <c r="E1061" t="n">
         <v>2.53999996185303</v>
       </c>
-      <c r="F1061"/>
+      <c r="F1061" t="n">
+        <v>2.53999996185303</v>
+      </c>
       <c r="G1061" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1062">
+      <c r="A1062" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B1062" t="n">
+        <v>500</v>
+      </c>
+      <c r="C1062" t="n">
+        <v>2.53999996185303</v>
+      </c>
+      <c r="D1062" t="n">
+        <v>2.53999996185303</v>
+      </c>
+      <c r="E1062" t="n">
+        <v>2.53999996185303</v>
+      </c>
+      <c r="F1062"/>
+      <c r="G1062" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/SIAV.MI.xlsx
+++ b/data/SIAV.MI.xlsx
@@ -24791,8 +24791,31 @@
       <c r="E1062" t="n">
         <v>2.53999996185303</v>
       </c>
-      <c r="F1062"/>
+      <c r="F1062" t="n">
+        <v>2.53999996185303</v>
+      </c>
       <c r="G1062" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1063">
+      <c r="A1063" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B1063" t="n">
+        <v>6500</v>
+      </c>
+      <c r="C1063" t="n">
+        <v>2.57999992370605</v>
+      </c>
+      <c r="D1063" t="n">
+        <v>2.53999996185303</v>
+      </c>
+      <c r="E1063" t="n">
+        <v>2.53999996185303</v>
+      </c>
+      <c r="F1063"/>
+      <c r="G1063" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/SIAV.MI.xlsx
+++ b/data/SIAV.MI.xlsx
@@ -24821,6 +24821,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1064">
+      <c r="A1064" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B1064" t="n">
+        <v>19000</v>
+      </c>
+      <c r="C1064" t="n">
+        <v>2.66000008583069</v>
+      </c>
+      <c r="D1064" t="n">
+        <v>2.51999998092651</v>
+      </c>
+      <c r="E1064" t="n">
+        <v>2.51999998092651</v>
+      </c>
+      <c r="F1064" t="n">
+        <v>2.66000008583069</v>
+      </c>
+      <c r="G1064" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SIAV.MI.xlsx
+++ b/data/SIAV.MI.xlsx
@@ -28091,6 +28091,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1067">
+      <c r="A1067" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B1067" t="n">
+        <v>2500</v>
+      </c>
+      <c r="C1067" t="n">
+        <v>2.53999996185303</v>
+      </c>
+      <c r="D1067" t="n">
+        <v>2.53999996185303</v>
+      </c>
+      <c r="E1067" t="n">
+        <v>2.53999996185303</v>
+      </c>
+      <c r="F1067" t="n">
+        <v>2.53999996185303</v>
+      </c>
+      <c r="G1067" t="n">
+        <v>2.53999996185303</v>
+      </c>
+      <c r="H1067" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SIAV.MI.xlsx
+++ b/data/SIAV.MI.xlsx
@@ -28117,6 +28117,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1068">
+      <c r="A1068" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B1068" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C1068" t="n">
+        <v>2.57999992370605</v>
+      </c>
+      <c r="D1068" t="n">
+        <v>2.51999998092651</v>
+      </c>
+      <c r="E1068" t="n">
+        <v>2.57999992370605</v>
+      </c>
+      <c r="F1068" t="n">
+        <v>2.51999998092651</v>
+      </c>
+      <c r="G1068" t="n">
+        <v>2.51999998092651</v>
+      </c>
+      <c r="H1068" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SIAV.MI.xlsx
+++ b/data/SIAV.MI.xlsx
@@ -31350,6 +31350,64 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1069">
+      <c r="A1069" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1069" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C1069" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D1069" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E1069" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F1069" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G1069" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H1069" t="n">
+        <v>500</v>
+      </c>
+      <c r="I1069" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1070">
+      <c r="A1070" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1070" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C1070" t="n">
+        <v>2.46000003814697</v>
+      </c>
+      <c r="D1070" t="n">
+        <v>2.55999994277954</v>
+      </c>
+      <c r="E1070" t="n">
+        <v>2.40000009536743</v>
+      </c>
+      <c r="F1070" t="n">
+        <v>2.48000001907349</v>
+      </c>
+      <c r="G1070" t="n">
+        <v>2.48000001907349</v>
+      </c>
+      <c r="H1070" t="n">
+        <v>10500</v>
+      </c>
+      <c r="I1070" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SIAV.MI.xlsx
+++ b/data/SIAV.MI.xlsx
@@ -31408,6 +31408,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1071">
+      <c r="A1071" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1071" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C1071" t="n">
+        <v>2.51999998092651</v>
+      </c>
+      <c r="D1071" t="n">
+        <v>2.51999998092651</v>
+      </c>
+      <c r="E1071" t="n">
+        <v>2.51999998092651</v>
+      </c>
+      <c r="F1071" t="n">
+        <v>2.51999998092651</v>
+      </c>
+      <c r="G1071" t="n">
+        <v>2.51999998092651</v>
+      </c>
+      <c r="H1071" t="n">
+        <v>500</v>
+      </c>
+      <c r="I1071" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SIAV.MI.xlsx
+++ b/data/SIAV.MI.xlsx
@@ -31437,6 +31437,64 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1072">
+      <c r="A1072" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1072" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C1072" t="n">
+        <v>2.51999998092651</v>
+      </c>
+      <c r="D1072" t="n">
+        <v>2.51999998092651</v>
+      </c>
+      <c r="E1072" t="n">
+        <v>2.51999998092651</v>
+      </c>
+      <c r="F1072" t="n">
+        <v>2.51999998092651</v>
+      </c>
+      <c r="G1072" t="n">
+        <v>2.51999998092651</v>
+      </c>
+      <c r="H1072" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1072" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1073">
+      <c r="A1073" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1073" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C1073" t="n">
+        <v>2.46000003814697</v>
+      </c>
+      <c r="D1073" t="n">
+        <v>2.46000003814697</v>
+      </c>
+      <c r="E1073" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="F1073" t="n">
+        <v>2.40000009536743</v>
+      </c>
+      <c r="G1073" t="n">
+        <v>2.40000009536743</v>
+      </c>
+      <c r="H1073" t="n">
+        <v>37500</v>
+      </c>
+      <c r="I1073" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SIAV.MI.xlsx
+++ b/data/SIAV.MI.xlsx
@@ -31495,6 +31495,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1074">
+      <c r="A1074" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1074" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C1074" t="n">
+        <v>2.35999989509583</v>
+      </c>
+      <c r="D1074" t="n">
+        <v>2.38000011444092</v>
+      </c>
+      <c r="E1074" t="n">
+        <v>2.29999995231628</v>
+      </c>
+      <c r="F1074" t="n">
+        <v>2.38000011444092</v>
+      </c>
+      <c r="G1074" t="n">
+        <v>2.38000011444092</v>
+      </c>
+      <c r="H1074" t="n">
+        <v>11500</v>
+      </c>
+      <c r="I1074" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SIAV.MI.xlsx
+++ b/data/SIAV.MI.xlsx
@@ -31524,6 +31524,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1075">
+      <c r="A1075" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1075" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C1075" t="n">
+        <v>2.3199999332428</v>
+      </c>
+      <c r="D1075" t="n">
+        <v>2.44000005722046</v>
+      </c>
+      <c r="E1075" t="n">
+        <v>2.24000000953674</v>
+      </c>
+      <c r="F1075" t="n">
+        <v>2.48000001907349</v>
+      </c>
+      <c r="G1075" t="n">
+        <v>2.48000001907349</v>
+      </c>
+      <c r="H1075" t="n">
+        <v>15500</v>
+      </c>
+      <c r="I1075" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SIAV.MI.xlsx
+++ b/data/SIAV.MI.xlsx
@@ -31535,7 +31535,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="D1075" t="n">
-        <v>2.44000005722046</v>
+        <v>2.48000001907349</v>
       </c>
       <c r="E1075" t="n">
         <v>2.24000000953674</v>
@@ -31550,6 +31550,35 @@
         <v>15500</v>
       </c>
       <c r="I1075" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1076">
+      <c r="A1076" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1076" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C1076" t="n">
+        <v>2.44000005722046</v>
+      </c>
+      <c r="D1076" t="n">
+        <v>2.44000005722046</v>
+      </c>
+      <c r="E1076" t="n">
+        <v>2.33999991416931</v>
+      </c>
+      <c r="F1076" t="n">
+        <v>2.35999989509583</v>
+      </c>
+      <c r="G1076" t="n">
+        <v>2.35999989509583</v>
+      </c>
+      <c r="H1076" t="n">
+        <v>21000</v>
+      </c>
+      <c r="I1076" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SIAV.MI.xlsx
+++ b/data/SIAV.MI.xlsx
@@ -31582,6 +31582,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1077">
+      <c r="A1077" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1077" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C1077" t="n">
+        <v>2.33999991416931</v>
+      </c>
+      <c r="D1077" t="n">
+        <v>2.35999989509583</v>
+      </c>
+      <c r="E1077" t="n">
+        <v>2.27999997138977</v>
+      </c>
+      <c r="F1077" t="n">
+        <v>2.33999991416931</v>
+      </c>
+      <c r="G1077" t="n">
+        <v>2.33999991416931</v>
+      </c>
+      <c r="H1077" t="n">
+        <v>9000</v>
+      </c>
+      <c r="I1077" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SIAV.MI.xlsx
+++ b/data/SIAV.MI.xlsx
@@ -31611,6 +31611,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1078">
+      <c r="A1078" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1078" s="1" t="n">
+        <v>46325.3333333333</v>
+      </c>
+      <c r="C1078" t="n">
+        <v>2.27999997138977</v>
+      </c>
+      <c r="D1078" t="n">
+        <v>2.27999997138977</v>
+      </c>
+      <c r="E1078" t="n">
+        <v>2.27999997138977</v>
+      </c>
+      <c r="F1078" t="n">
+        <v>2.27999997138977</v>
+      </c>
+      <c r="G1078" t="n">
+        <v>2.27999997138977</v>
+      </c>
+      <c r="H1078" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I1078" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
